--- a/task/关键标准答案.xlsx
+++ b/task/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="Rc3ff38ef31ff4eb8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R3a43094cd33a4833"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="Rb9ef2eece930497c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Ra85dd76fbbe44546"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R672cb93373684d88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R5775463b8e124579"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="Rf85b8145a2da4cfb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R1a60970b0b6048dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Rccc398d6c94a413a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Red69459362bb44f6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -397,43 +397,29 @@
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="5" t="str">
-        <x:v>本地构建入口</x:v>
+        <x:v>发布说明</x:v>
       </x:c>
       <x:c r="B9" s="5" t="str">
-        <x:v>output/tools/build_delivery.py</x:v>
+        <x:v>output/RELEASE-NOTES.md</x:v>
       </x:c>
       <x:c r="C9" s="5" t="str">
-        <x:v>从业务材料生成交付</x:v>
+        <x:v>记录上线顺序、观察和回退</x:v>
       </x:c>
       <x:c r="D9" s="5" t="str">
-        <x:v>在Windows11空目录运行</x:v>
+        <x:v>与迁移策略互证</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
-      <x:c r="A10" s="5" t="str">
-        <x:v>发布说明</x:v>
-      </x:c>
-      <x:c r="B10" s="5" t="str">
-        <x:v>output/RELEASE-NOTES.md</x:v>
-      </x:c>
-      <x:c r="C10" s="5" t="str">
-        <x:v>记录岗位接续与现场边界</x:v>
-      </x:c>
-      <x:c r="D10" s="5" t="str">
-        <x:v>与候选材料互证</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="15" hidden="0" customHeight="1">
-      <x:c r="A11" s="6" t="str">
+      <x:c r="A10" s="6" t="str">
         <x:v>结果说明</x:v>
       </x:c>
-      <x:c r="B11" s="6" t="str">
+      <x:c r="B10" s="6" t="str">
         <x:v>output/README.txt</x:v>
       </x:c>
-      <x:c r="C11" s="6" t="str">
+      <x:c r="C10" s="6" t="str">
         <x:v>说明各目录用途</x:v>
       </x:c>
-      <x:c r="D11" s="6" t="str">
+      <x:c r="D10" s="6" t="str">
         <x:v>与实际路径互证</x:v>
       </x:c>
     </x:row>
